--- a/docs/test-cases/SPM-86_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-86_Test_Cases.xlsx
@@ -28,7 +28,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -62,6 +62,9 @@
       <name val="Arial"/>
       <color theme="1"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -158,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -223,6 +226,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -515,12 +521,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="44.25" customHeight="1" s="25">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="28" t="inlineStr">
         <is>
           <t>SPM-86: As the assigned Event Coordinator, I want to submit an event for an Operational Safety Check once its venue and technical arrangements are confirmed so that the Safety Officer can review it before the event proceeds</t>
         </is>
@@ -532,32 +538,32 @@
     </row>
     <row r="2" ht="12.75" customHeight="1" s="25"/>
     <row r="3" ht="12.75" customHeight="1" s="25">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>Linked AC</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="28" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -584,27 +590,27 @@
           <t>TC01</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC01</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>An event whose venue and equipment are both held can be submitted for a safety check</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>AC1, AC3, AC5</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -623,27 +629,27 @@
           <t>TC02</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC02</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>The submission is recorded with who submitted it and when, and the event cannot be submitted again</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>AC8, AC6</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -662,27 +668,27 @@
           <t>TC03</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC03</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>The Event Organiser sees that their event is in Safety review</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -701,38 +707,42 @@
           <t>TC04</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC04</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>Technical Support and the Operations Manager see the Safety review status</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H7" s="29" t="n"/>
-      <c r="I7" s="29" t="n"/>
+      <c r="I7" s="29" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="25">
       <c r="A8" s="5" t="inlineStr">
@@ -740,27 +750,27 @@
           <t>TC05</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC05</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Equipment Technical Support could only partly supply still allows submission</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>AC1, AC3</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -779,27 +789,27 @@
           <t>TC06</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC06</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>Submission is refused while a venue request and an equipment request are still outstanding, and each is named</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -818,27 +828,27 @@
           <t>TC07</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC07</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>Submission is refused while an approved venue booking is flagged for review, and the reason is given</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="29" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -857,27 +867,27 @@
           <t>TC08</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC08</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>Submission is refused while reserved equipment is flagged for review, and the item is named</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -896,27 +906,27 @@
           <t>TC09</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC09</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>A second submission from a page opened before the first is refused</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="29" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -935,38 +945,42 @@
           <t>TC10</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC10</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>Only the assigned Coordinator is offered the submission</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H13" s="29" t="n"/>
-      <c r="I13" s="29" t="n"/>
+      <c r="I13" s="29" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="12.75" customHeight="1" s="25">
       <c r="A14" s="5" t="inlineStr">
@@ -974,27 +988,27 @@
           <t>TC11</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC11</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>An Approved event that has not begun planning cannot be submitted</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1013,27 +1027,27 @@
           <t>TC12</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC12</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>Equipment the Coordinator marked as not required does not stop submission</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D15" s="29" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F15" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1052,27 +1066,27 @@
           <t>TC13</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC13</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>The Safety Officer is notified when an event is submitted</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F16" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1088,19 +1102,19 @@
     <row r="17" ht="12.75" customHeight="1" s="25"/>
     <row r="18" ht="12.75" customHeight="1" s="25"/>
     <row r="19" ht="12.75" customHeight="1" s="25">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
       <c r="C19" s="26" t="n"/>
       <c r="D19" s="27" t="n"/>
-      <c r="E19" s="1" t="inlineStr">
+      <c r="E19" s="28" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
@@ -1108,19 +1122,19 @@
       <c r="F19" s="27" t="n"/>
     </row>
     <row r="20" ht="57.75" customHeight="1" s="25">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>Given all of the event's required venue bookings are confirmed and its equipment arrangements are reserved or marked as not required, when the Coordinator views the event, then they can submit it for an Operational Safety Check.</t>
         </is>
       </c>
       <c r="C20" s="26" t="n"/>
       <c r="D20" s="27" t="n"/>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC01
 SPM-86-TC05
@@ -1131,19 +1145,19 @@
       <c r="F20" s="27" t="n"/>
     </row>
     <row r="21" ht="57.75" customHeight="1" s="25">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Given a required venue booking or equipment arrangement is still outstanding or flagged for review, when the Coordinator attempts to submit, then submission is refused and the outstanding arrangement is identified.</t>
         </is>
       </c>
       <c r="C21" s="26" t="n"/>
       <c r="D21" s="27" t="n"/>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E21" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC06
 SPM-86-TC07
@@ -1153,19 +1167,19 @@
       <c r="F21" s="27" t="n"/>
     </row>
     <row r="22" ht="30.75" customHeight="1" s="25">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="29" t="inlineStr">
         <is>
           <t>Submitting changes the event status to Safety Review.</t>
         </is>
       </c>
       <c r="C22" s="26" t="n"/>
       <c r="D22" s="27" t="n"/>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E22" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC01
 SPM-86-TC05</t>
@@ -1174,19 +1188,19 @@
       <c r="F22" s="27" t="n"/>
     </row>
     <row r="23" ht="30.75" customHeight="1" s="25">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>The Safety Review status is visible to the Event Organiser and other users who can view the event's status.</t>
         </is>
       </c>
       <c r="C23" s="26" t="n"/>
       <c r="D23" s="27" t="n"/>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC03
 SPM-86-TC04</t>
@@ -1195,19 +1209,19 @@
       <c r="F23" s="27" t="n"/>
     </row>
     <row r="24" ht="30.75" customHeight="1" s="25">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>The Safety Officer is notified when an event is submitted for a safety check.</t>
         </is>
       </c>
       <c r="C24" s="26" t="n"/>
       <c r="D24" s="27" t="n"/>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="E24" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC01
 SPM-86-TC13</t>
@@ -1216,19 +1230,19 @@
       <c r="F24" s="27" t="n"/>
     </row>
     <row r="25" ht="30.75" customHeight="1" s="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>An event cannot be submitted again while a safety check is already pending for it.</t>
         </is>
       </c>
       <c r="C25" s="26" t="n"/>
       <c r="D25" s="27" t="n"/>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="E25" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC02
 SPM-86-TC09</t>
@@ -1237,19 +1251,19 @@
       <c r="F25" s="27" t="n"/>
     </row>
     <row r="26" ht="30.75" customHeight="1" s="25">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>Only the assigned Event Coordinator can submit the event for a safety check.</t>
         </is>
       </c>
       <c r="C26" s="26" t="n"/>
       <c r="D26" s="27" t="n"/>
-      <c r="E26" s="18" t="inlineStr">
+      <c r="E26" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC10</t>
         </is>
@@ -1257,19 +1271,19 @@
       <c r="F26" s="27" t="n"/>
     </row>
     <row r="27" ht="30.75" customHeight="1" s="25">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>AC8</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
         <is>
           <t>The date and time of submission and who submitted it are recorded against the event.</t>
         </is>
       </c>
       <c r="C27" s="26" t="n"/>
       <c r="D27" s="27" t="n"/>
-      <c r="E27" s="18" t="inlineStr">
+      <c r="E27" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC02</t>
         </is>
@@ -1278,12 +1292,12 @@
     </row>
     <row r="28" ht="12.75" customHeight="1" s="25"/>
     <row r="29" ht="165.75" customHeight="1" s="25">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t>src/lib/safetyCheck.ts
 src/app/api/events/[id]/safety-check/route.ts
@@ -2346,7 +2360,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC09</t>
         </is>
@@ -2358,7 +2372,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>npm run fixtures:spm86 has been run. 'SPM86 Two Tabs Submit' is in Planning, assigned to Daniel Tan, with an approved venue booking and its Handheld Wireless Mic Reserved. Logged in as Daniel Tan. This case changes the event's status - run npm run fixtures:spm86 afterwards.</t>
         </is>
@@ -2370,7 +2384,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
 2. Click 'SPM86 Two Tabs Submit' in the list
@@ -2387,7 +2401,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Event: SPM86 Two Tabs Submit (Planning)
 Two browser tabs on the same event</t>
@@ -2400,7 +2414,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Step 4: The second tab shows 'The event has been submitted for a safety check. The Safety Officer has been notified.' and the badge 'Safety review'.
 Step 6: The first tab shows 'A safety check is already pending for this event.' Nothing else changes - the event was submitted once, not twice.</t>
@@ -2413,7 +2427,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -2445,7 +2459,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Step 4: The second tab shows 'The event has been submitted for a safety check. The Safety Officer has been notified.' and the badge 'Safety review'.
 Step 6: The first tab shows 'A safety check is already pending for this event.' Nothing else changes - the event was submitted once, not twice.</t>
@@ -2482,7 +2496,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -2513,7 +2527,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Step 4: The second tab shows 'The event has been submitted for a safety check. The Safety Officer has been notified.' and the badge 'Safety review'.
 Step 6: The first tab shows 'A safety check is already pending for this event.' Nothing else changes - the event was submitted once, not twice.</t>
@@ -3556,7 +3570,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.88" customWidth="1" style="25" min="1" max="1"/>
@@ -3564,45 +3578,52 @@
     <col width="12.63" customWidth="1" style="25" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="25">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="25">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="25">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="9" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="25">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="18" t="inlineStr">
-        <is>
-          <t>SPM-86-TC10</t>
-        </is>
-      </c>
+      <c r="B2" s="9" t="n"/>
     </row>
     <row r="3" ht="84.75" customHeight="1" s="25">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="18" t="inlineStr">
-        <is>
-          <t>npm run fixtures:spm86 has been run. 'SPM86 Another Coordinator' is in Planning with an approved venue booking and its Handheld Wireless Mic Reserved - nothing outstanding - but is assigned to Priya Raj, not Daniel Tan. Logged in as Event Coordinator Daniel Tan (daniel.tan@connectsphere.com / password123).</t>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>SPM-86-TC10</t>
         </is>
       </c>
     </row>
     <row r="4" ht="84.75" customHeight="1" s="25">
       <c r="A4" s="10" t="inlineStr">
         <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>npm run fixtures:spm86 has been run. 'SPM86 Another Coordinator' is in Planning with an approved venue booking and its Handheld Wireless Mic Reserved - nothing outstanding - but is assigned to Priya Raj, not Daniel Tan. Logged in as Event Coordinator Daniel Tan (daniel.tan@connectsphere.com / password123).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="57.75" customHeight="1" s="25">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
 2. Click 'SPM86 Another Coordinator' in the list
@@ -3613,13 +3634,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="57.75" customHeight="1" s="25">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="6" ht="71.25" customHeight="1" s="25">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Event: SPM86 Another Coordinator (Planning, assigned to Priya Raj)
 Coordinator: daniel.tan@connectsphere.com
@@ -3627,179 +3648,178 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="71.25" customHeight="1" s="25">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="7" ht="17.25" customHeight="1" s="25">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Step 2: The event opens and Daniel Tan can read it, but there is no 'Submit for safety check' button - the arrangements are all held, so only the assignment is stopping him.
 Step 6: Grace Lim can read the event but has no 'Submit for safety check' button either.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="25">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>Janelle</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="15.75" customHeight="1" s="25">
       <c r="A8" s="10" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="25">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B9" s="16" t="n">
         <v>46304</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="25"/>
-    <row r="10" ht="15.75" customHeight="1" s="25">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="25"/>
+    <row r="11" ht="15.75" customHeight="1" s="25">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="25">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="25">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>Step 2: The event opens and Daniel Tan can read it, but there is no 'Submit for safety check' button - the arrangements are all held, so only the assignment is stopping him.
 Step 6: Grace Lim can read the event but has no 'Submit for safety check' button either.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="25">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="25">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="25">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>Janelle</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="25">
       <c r="A15" s="17" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="25">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B16" s="16" t="n">
         <v>46304</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="25"/>
-    <row r="17" ht="15.75" customHeight="1" s="25">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="25"/>
+    <row r="18" ht="15.75" customHeight="1" s="25">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="25">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="B18" s="13" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="25">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>Step 2: The event opens and Daniel Tan can read it, but there is no 'Submit for safety check' button - the arrangements are all held, so only the assignment is stopping him.
 Step 6: Grace Lim can read the event but has no 'Submit for safety check' button either.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="25">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="25">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="25">
       <c r="A21" s="17" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="25">
       <c r="A22" s="17" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="25">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B23" s="22" t="n">
         <v>46305</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="25"/>
     <row r="24" ht="15.75" customHeight="1" s="25"/>
     <row r="25" ht="15.75" customHeight="1" s="25"/>
     <row r="26" ht="15.75" customHeight="1" s="25"/>
@@ -4778,6 +4798,9 @@
     <row r="999" ht="15.75" customHeight="1" s="25"/>
     <row r="1000" ht="15.75" customHeight="1" s="25"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -4811,7 +4834,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC11</t>
         </is>
@@ -4823,7 +4846,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>npm run fixtures:spm86 has been run. 'SPM86 Not Yet Planning' is Approved (planning has not begun - no venue or equipment requested yet) and assigned to Daniel Tan. Logged in as Daniel Tan.</t>
         </is>
@@ -4835,7 +4858,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
 2. Click 'SPM86 Not Yet Planning' in the list</t>
@@ -4848,7 +4871,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Event: SPM86 Not Yet Planning (Approved)</t>
         </is>
@@ -4860,7 +4883,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Step 2: The event opens with the status badge 'Approved' and there is no 'Submit for safety check' button - an event is submitted from Planning, once its arrangements have been made.</t>
         </is>
@@ -4872,7 +4895,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -4904,7 +4927,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Step 2: The event opens with the status badge 'Approved' and there is no 'Submit for safety check' button - an event is submitted from Planning, once its arrangements have been made.</t>
         </is>
@@ -4940,7 +4963,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -4971,7 +4994,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Step 2: The event opens with the status badge 'Approved' and there is no 'Submit for safety check' button - an event is submitted from Planning, once its arrangements have been made.</t>
         </is>
@@ -6035,7 +6058,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC12</t>
         </is>
@@ -6047,7 +6070,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>npm run fixtures:spm86 has been run. 'SPM86 Arrangements Outstanding' is in Planning, assigned to Daniel Tan, with a venue booking request at Orchard Seminar Room that is still Pending, Handheld Wireless Mic Reserved and Audio Mixing Desk Requested. This case changes the event - run npm run fixtures:spm86 afterwards.</t>
         </is>
@@ -6060,7 +6083,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Log in as marcus.wong@connectsphere.com with password123
 2. Click 'Booking Requests' in the sidebar
@@ -6083,7 +6106,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Event: SPM86 Arrangements Outstanding (Planning)
 Venue: Orchard Seminar Room, Pending → approved in step 3
@@ -6097,7 +6120,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Step 3: The request is approved.
 Step 9: The Audio Mixing Desk row's badge changes from 'Outstanding' to 'Not required', and its button changes to 'Mark as required'.
@@ -6111,7 +6134,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -6179,7 +6202,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -6278,7 +6301,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>Step 3: The request is approved.
 Step 9: The Audio Mixing Desk row's badge changes from 'Outstanding' to 'Not required', and its button changes to 'Mark as required'.
@@ -6316,7 +6339,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -6347,7 +6370,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B33" s="29" t="inlineStr">
         <is>
           <t>Step 3: The request is approved.
 Step 9: The Audio Mixing Desk row's badge changes from 'Outstanding' to 'Not required', and its button changes to 'Mark as required'.
@@ -6385,7 +6408,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B36" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -7398,7 +7421,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC13</t>
         </is>
@@ -7410,7 +7433,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>npm run fixtures:spm86 has been run (so 'SPM86 Harbour Safety Ready' is in Planning with everything held). Logged in as Event Coordinator Daniel Tan (daniel.tan@connectsphere.com / password123). This case changes the event's status - run npm run fixtures:spm86 afterwards.</t>
         </is>
@@ -7422,7 +7445,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
 2. Click 'SPM86 Harbour Safety Ready' in the list
@@ -7441,7 +7464,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Event: SPM86 Harbour Safety Ready (Planning)
 Coordinator: daniel.tan@connectsphere.com
@@ -7455,7 +7478,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Step 4: The message 'The event has been submitted for a safety check. The Safety Officer has been notified.' is shown and the status badge changes to 'Safety review'.
 Step 7: The Notifications list has a new notification titled 'Event submitted for safety check', reading 'SPM86 Harbour Safety Ready (&lt;reference from step 3&gt;) is ready for an Operational Safety Check.'
@@ -7469,7 +7492,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -7537,7 +7560,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -7635,7 +7658,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="29" t="inlineStr">
         <is>
           <t>Step 4: The message 'The event has been submitted for a safety check. The Safety Officer has been notified.' is shown and the status badge changes to 'Safety review'.
 Step 7: The Notifications list has a new notification titled 'Event submitted for safety check', reading 'SPM86 Harbour Safety Ready (&lt;reference from step 3&gt;) is ready for an Operational Safety Check.'
@@ -8694,7 +8717,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC01</t>
         </is>
@@ -8706,7 +8729,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>npm run fixtures:spm86 has been run. 'SPM86 Harbour Safety Ready' is in Planning, assigned to Daniel Tan, with an approved venue booking at Orchard Seminar Room and one equipment requirement (Handheld Wireless Mic) with status Reserved. Logged in as Event Coordinator Daniel Tan (daniel.tan@connectsphere.com / password123). This case changes the event's status - SPM-86-TC02, TC03 and TC04 read the result, so go straight to those and run npm run fixtures:spm86 after TC04.</t>
         </is>
@@ -8718,7 +8741,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
 2. Click 'SPM86 Harbour Safety Ready' in the list
@@ -8733,7 +8756,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Event: SPM86 Harbour Safety Ready (Planning)
 Venue: Orchard Seminar Room, booking Approved
@@ -8748,7 +8771,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Step 2: The event opens with the status badge 'Planning' and a 'Submit for safety check' button in the header.
 Step 3: A dialog headed 'Submit for safety check?' appears, saying the event will move to Safety review and the Safety Officer will be notified.
@@ -8762,7 +8785,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -8794,7 +8817,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Step 2: The event opens with the status badge 'Planning' and a 'Submit for safety check' button in the header.
 Step 3: A dialog headed 'Submit for safety check?' appears, saying the event will move to Safety review and the Safety Officer will be notified.
@@ -8863,7 +8886,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Step 2: The event opens with the status badge 'Planning' and a 'Submit for safety check' button in the header.
 Step 3: A dialog headed 'Submit for safety check?' appears, saying the event will move to Safety review and the Safety Officer will be notified.
@@ -9929,7 +9952,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC02</t>
         </is>
@@ -9941,7 +9964,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC01 has just been run (so 'SPM86 Harbour Safety Ready' is in Safety review) and the fixtures have NOT been reset since. Still logged in as Daniel Tan, on the event's page. Note the date and time TC01 step 4 was done.</t>
         </is>
@@ -9953,7 +9976,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Reload the page in the browser</t>
         </is>
@@ -9965,7 +9988,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Event: SPM86 Harbour Safety Ready, now Safety review
 Submitted by: Daniel Tan</t>
@@ -9978,7 +10001,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Step 1: The status badge still reads 'Safety review' after reloading, and there is no 'Submit for safety check' button anywhere on the page - a safety check is already pending. In the 'Details' card, the row under 'Status' is 'Safety check', reading 'Awaiting review · submitted by Daniel Tan, &lt;date and time of TC01 step 4&gt;' (e.g. 'Awaiting review · submitted by Daniel Tan, 9 Oct 2026, 14:30'), in Singapore time.</t>
         </is>
@@ -9990,7 +10013,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -10022,7 +10045,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Step 1: The status badge still reads 'Safety review' after reloading, and there is no 'Submit for safety check' button anywhere on the page - a safety check is already pending. In the 'Details' card, the row under 'Status' is 'Safety check', reading 'Awaiting review · submitted by Daniel Tan, &lt;date and time of TC01 step 4&gt;' (e.g. 'Awaiting review · submitted by Daniel Tan, 9 Oct 2026, 14:30'), in Singapore time.</t>
         </is>
@@ -10089,7 +10112,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Step 1: The status badge still reads 'Safety review' after reloading, and there is no 'Submit for safety check' button anywhere on the page - a safety check is already pending. In the 'Details' card, the row under 'Status' is 'Safety check', reading 'Awaiting review · submitted by Daniel Tan, &lt;date and time of TC01 step 4&gt;' (e.g. 'Awaiting review · submitted by Daniel Tan, 9 Oct 2026, 14:30'), in Singapore time.</t>
         </is>
@@ -11153,7 +11176,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC03</t>
         </is>
@@ -11165,7 +11188,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC02 has just been run (so 'SPM86 Harbour Safety Ready' is in Safety review) and the fixtures have NOT been reset since. Rachel Ng (rachel.ng@meridianfina.com / password123) is the Event Organiser who raised it.</t>
         </is>
@@ -11177,7 +11200,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Click 'Log out' in the top bar
 2. Log in as rachel.ng@meridianfina.com with password123
@@ -11192,7 +11215,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Account: rachel.ng@meridianfina.com (Event Organiser)
 Event: SPM86 Harbour Safety Ready, Safety review</t>
@@ -11205,7 +11228,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Step 2: The Dashboard opens and 'SPM86 Harbour Safety Ready' is listed under a 'Safety review' heading.
 Step 3: 'SPM86 Harbour Safety Ready' appears in the organiser's list with the status 'Safety review'.
@@ -11219,7 +11242,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -11251,7 +11274,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Step 2: The Dashboard opens and 'SPM86 Harbour Safety Ready' is listed under a 'Safety review' heading.
 Step 3: 'SPM86 Harbour Safety Ready' appears in the organiser's list with the status 'Safety review'.
@@ -11299,7 +11322,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -11320,7 +11343,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Step 2: The Dashboard opens and 'SPM86 Harbour Safety Ready' is listed under a 'Safety review' heading.
 Step 3: 'SPM86 Harbour Safety Ready' appears in the organiser's list with the status 'Safety review'.
@@ -11368,7 +11391,7 @@
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -12364,7 +12387,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.88" customWidth="1" style="25" min="1" max="1"/>
@@ -12372,45 +12395,52 @@
     <col width="12.63" customWidth="1" style="25" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="25">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="25">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="25">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="9" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="25">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="18" t="inlineStr">
-        <is>
-          <t>SPM-86-TC04</t>
-        </is>
-      </c>
+      <c r="B2" s="9" t="n"/>
     </row>
     <row r="3" ht="44.25" customHeight="1" s="25">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B3" s="18" t="inlineStr">
-        <is>
-          <t>SPM-86-TC03 has just been run (so 'SPM86 Harbour Safety Ready' is in Safety review) and the fixtures have NOT been reset since. Run npm run fixtures:spm86 after this case.</t>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>SPM-86-TC04</t>
         </is>
       </c>
     </row>
     <row r="4" ht="84.75" customHeight="1" s="25">
       <c r="A4" s="10" t="inlineStr">
         <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>SPM-86-TC03 has just been run (so 'SPM86 Harbour Safety Ready' is in Safety review) and the fixtures have NOT been reset since. Run npm run fixtures:spm86 after this case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.25" customHeight="1" s="25">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>1. Click 'Log out' in the top bar
 2. Log in as kenji.sato@connectsphere.com with password123
@@ -12418,13 +12448,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="44.25" customHeight="1" s="25">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="6" ht="125.25" customHeight="1" s="25">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Technical Support: kenji.sato@connectsphere.com
 Operations Manager: grace.lim@connectsphere.com
@@ -12432,179 +12462,178 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="125.25" customHeight="1" s="25">
-      <c r="A6" s="10" t="inlineStr">
+    <row r="7" ht="17.25" customHeight="1" s="25">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Step 2: Kenji Sato's Dashboard lists 'SPM86 Harbour Safety Ready' under 'Upcoming events' with the badge 'Safety review'.
 Step 3: The Equipment Requests list still includes 'SPM86 Harbour Safety Ready', with 'Safety review' in the 'Event status' column - Technical Support keep sight of the reserved mic while the check is pending.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="25">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>Janelle</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="15.75" customHeight="1" s="25">
       <c r="A8" s="10" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="25">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B9" s="16" t="n">
         <v>46304</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="25"/>
-    <row r="10" ht="15.75" customHeight="1" s="25">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="25"/>
+    <row r="11" ht="15.75" customHeight="1" s="25">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="14" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="25">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="25">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>Step 2: Kenji Sato's Dashboard lists 'SPM86 Harbour Safety Ready' under 'Upcoming events' with the badge 'Safety review'.
 Step 3: The Equipment Requests list still includes 'SPM86 Harbour Safety Ready', with 'Safety review' in the 'Event status' column - Technical Support keep sight of the reserved mic while the check is pending.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="25">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="25">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="25">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>Janelle</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="25">
       <c r="A15" s="17" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="25">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B16" s="16" t="n">
         <v>46304</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="25"/>
-    <row r="17" ht="15.75" customHeight="1" s="25">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="17" ht="15.75" customHeight="1" s="25"/>
+    <row r="18" ht="15.75" customHeight="1" s="25">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="25">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="B18" s="13" t="n"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" s="25">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>Step 2: Kenji Sato's Dashboard lists 'SPM86 Harbour Safety Ready' under 'Upcoming events' with the badge 'Safety review'.
 Step 3: The Equipment Requests list still includes 'SPM86 Harbour Safety Ready', with 'Safety review' in the 'Event status' column - Technical Support keep sight of the reserved mic while the check is pending.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="25">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="15.75" customHeight="1" s="25">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="25">
       <c r="A21" s="17" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="25">
       <c r="A22" s="17" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="25">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B23" s="16" t="n">
         <v>46305</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="25"/>
     <row r="24" ht="15.75" customHeight="1" s="25"/>
     <row r="25" ht="15.75" customHeight="1" s="25"/>
     <row r="26" ht="15.75" customHeight="1" s="25"/>
@@ -13583,6 +13612,9 @@
     <row r="999" ht="15.75" customHeight="1" s="25"/>
     <row r="1000" ht="15.75" customHeight="1" s="25"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -13616,7 +13648,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC05</t>
         </is>
@@ -13628,7 +13660,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>npm run fixtures:spm86 has been run. 'SPM86 Partly Reserved Kit' is in Planning, assigned to Daniel Tan, with an approved venue booking and one equipment requirement for 2 Handheld Wireless Mics of which only 1 was reserved, leaving it at status Partially fulfilled. Logged in as Daniel Tan. This case changes the event's status - run npm run fixtures:spm86 afterwards.</t>
         </is>
@@ -13640,7 +13672,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
 2. Click 'SPM86 Partly Reserved Kit' in the list
@@ -13655,7 +13687,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Event: SPM86 Partly Reserved Kit (Planning)
 Equipment: Handheld Wireless Mic, 2 requested, 1 reserved (Partially fulfilled)</t>
@@ -13668,7 +13700,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Step 4: The message 'The event has been submitted for a safety check. The Safety Officer has been notified.' is shown and the status badge changes to 'Safety review' - a partly fulfilled request counts as arranged, the same as for Confirm event.</t>
         </is>
@@ -13680,7 +13712,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -13712,7 +13744,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Step 4: The message 'The event has been submitted for a safety check. The Safety Officer has been notified.' is shown and the status badge changes to 'Safety review' - a partly fulfilled request counts as arranged, the same as for Confirm event.</t>
         </is>
@@ -13748,7 +13780,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -13779,7 +13811,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Step 4: The message 'The event has been submitted for a safety check. The Safety Officer has been notified.' is shown and the status badge changes to 'Safety review' - a partly fulfilled request counts as arranged, the same as for Confirm event.</t>
         </is>
@@ -13815,7 +13847,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -14843,7 +14875,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC06</t>
         </is>
@@ -14855,7 +14887,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>npm run fixtures:spm86 has been run. 'SPM86 Arrangements Outstanding' is in Planning, assigned to Daniel Tan, with a venue booking request at Orchard Seminar Room that is still Pending, and two equipment requirements: Handheld Wireless Mic (Reserved) and Audio Mixing Desk (Requested, not yet reviewed). Logged in as Daniel Tan.</t>
         </is>
@@ -14867,7 +14899,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
 2. Click 'SPM86 Arrangements Outstanding' in the list
@@ -14882,7 +14914,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Event: SPM86 Arrangements Outstanding (Planning)
 Venue: Orchard Seminar Room, Pending
@@ -14896,7 +14928,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Step 2: The 'Submit for safety check' button is shown even though arrangements are outstanding(the venue is still pending and an equipment item isn't reserved).
 Step 4: The event is NOT submitted. The message 'This event cannot be submitted for a safety check yet: the venue for this event is still awaiting a decision from Venue Staff; Audio Mixing Desk for this event is not reserved yet.' is shown. The Handheld Wireless Mic, which is reserved, is not mentioned. The status badge still reads 'Planning'.</t>
@@ -14909,7 +14941,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -14941,7 +14973,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Step 2: The 'Submit for safety check' button is shown even though arrangements are outstanding.
 Step 4: The event is NOT submitted. The message 'This event cannot be submitted for a safety check yet: the venue for this event is still awaiting a decision from Venue Staff; Audio Mixing Desk for this event is not reserved yet.' is shown. The Handheld Wireless Mic, which is reserved, is not mentioned. The status badge still reads 'Planning'.</t>
@@ -14978,7 +15010,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -15009,7 +15041,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Step 2: The 'Submit for safety check' button is shown even though arrangements are outstanding.
 Step 4: The event is NOT submitted. The message 'This event cannot be submitted for a safety check yet: the venue for this event is still awaiting a decision from Venue Staff; Audio Mixing Desk for this event is not reserved yet.' is shown. The Handheld Wireless Mic, which is reserved, is not mentioned. The status badge still reads 'Planning'.</t>
@@ -15046,7 +15078,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -16074,7 +16106,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC07</t>
         </is>
@@ -16086,7 +16118,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>npm run fixtures:spm86 has been run. 'SPM86 Flagged Venue Booking' is in Planning, assigned to Daniel Tan. Its venue booking at Orchard Seminar Room is Approved but flagged for review because the event's date or time changed, and its Handheld Wireless Mic is Reserved. Logged in as Daniel Tan.</t>
         </is>
@@ -16098,7 +16130,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
 2. Click 'SPM86 Flagged Venue Booking' in the list
@@ -16113,7 +16145,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Event: SPM86 Flagged Venue Booking (Planning)
 Venue: Orchard Seminar Room, Approved, flagged for review (date or time changed)
@@ -16127,7 +16159,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Step 4: The event is NOT submitted. The message 'This event cannot be submitted for a safety check yet: the venue booking at Orchard Seminar Room for this event is flagged for review (the date or time changed).' is shown - an approved booking still blocks submission while it is flagged. The status badge still reads 'Planning'.</t>
         </is>
@@ -16139,7 +16171,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -16171,7 +16203,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Step 4: The event is NOT submitted. The message 'This event cannot be submitted for a safety check yet: the venue booking at Orchard Seminar Room for this event is flagged for review (the date or time changed).' is shown - an approved booking still blocks submission while it is flagged. The status badge still reads 'Planning'.</t>
         </is>
@@ -16238,7 +16270,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Step 4: The event is NOT submitted. The message 'This event cannot be submitted for a safety check yet: the venue booking at Orchard Seminar Room for this event is flagged for review (the date or time changed).' is shown - an approved booking still blocks submission while it is flagged. The status badge still reads 'Planning'.</t>
         </is>
@@ -17302,7 +17334,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>SPM-86-TC08</t>
         </is>
@@ -17314,7 +17346,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>npm run fixtures:spm86 has been run. 'SPM86 Flagged Equipment' is in Planning, assigned to Daniel Tan, with an approved venue booking at Orchard Seminar Room that is not flagged. Its Handheld Wireless Mic is Reserved but flagged for review because the event's date or time changed. Logged in as Daniel Tan.</t>
         </is>
@@ -17326,7 +17358,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
 2. Click 'SPM86 Flagged Equipment' in the list
@@ -17341,7 +17373,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Event: SPM86 Flagged Equipment (Planning)
 Venue: Orchard Seminar Room, Approved
@@ -17355,7 +17387,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Step 4: The event is NOT submitted. The message 'This event cannot be submitted for a safety check yet: Handheld Wireless Mic for this event is flagged for review (the date or time changed).' is shown, and the venue booking is not mentioned. The status badge still reads 'Planning'.</t>
         </is>
@@ -17367,7 +17399,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Janelle</t>
         </is>
@@ -17399,7 +17431,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>Step 4: The event is NOT submitted. The message 'This event cannot be submitted for a safety check yet: Handheld Wireless Mic for this event is flagged for review (the date or time changed).' is shown, and the venue booking is not mentioned. The status badge still reads 'Planning'.</t>
         </is>
@@ -17466,7 +17498,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Step 4: The event is NOT submitted. The message 'This event cannot be submitted for a safety check yet: Handheld Wireless Mic for this event is flagged for review (the date or time changed).' is shown, and the venue booking is not mentioned. The status badge still reads 'Planning'.</t>
         </is>
